--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4904,7 +4904,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>175</v>
       </c>
@@ -4919,13 +4919,13 @@
         <v>62</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5007,7 +5007,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>179</v>
       </c>
@@ -5022,13 +5022,13 @@
         <v>180</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5316,7 +5316,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>193</v>
       </c>
@@ -5337,7 +5337,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="309">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -820,6 +820,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Act.statusCode</t>
@@ -7045,7 +7049,7 @@
         <v>74</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>74</v>
+        <v>263</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>74</v>
@@ -7053,10 +7057,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7082,10 +7086,10 @@
         <v>91</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7116,7 +7120,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
@@ -7134,7 +7138,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7154,10 +7158,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7255,10 +7259,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7299,7 +7303,7 @@
         <v>74</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>74</v>
@@ -7358,10 +7362,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7461,10 +7465,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7564,10 +7568,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7667,10 +7671,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7770,10 +7774,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7871,10 +7875,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7972,10 +7976,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8075,10 +8079,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8178,10 +8182,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8281,10 +8285,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8307,7 +8311,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8360,7 +8364,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8380,10 +8384,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8406,7 +8410,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8439,7 +8443,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -8457,7 +8461,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8477,10 +8481,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8536,25 +8540,25 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8574,10 +8578,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8600,7 +8604,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8653,7 +8657,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8673,10 +8677,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8699,7 +8703,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8752,7 +8756,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8772,10 +8776,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8798,7 +8802,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8851,7 +8855,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8871,10 +8875,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8897,7 +8901,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -8950,7 +8954,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -8970,10 +8974,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8996,7 +9000,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9049,7 +9053,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9069,10 +9073,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9095,7 +9099,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9148,7 +9152,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9168,10 +9172,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9194,7 +9198,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9247,7 +9251,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9267,10 +9271,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9293,7 +9297,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9346,7 +9350,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9366,10 +9370,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9392,7 +9396,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9445,7 +9449,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9465,10 +9469,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9491,7 +9495,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9544,7 +9548,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9564,10 +9568,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9590,7 +9594,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9643,7 +9647,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-commentaire-er.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
